--- a/output/pdf_financials_xlsx/AUEN.xlsx
+++ b/output/pdf_financials_xlsx/AUEN.xlsx
@@ -3048,25 +3048,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.183365</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.319551</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.471475</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.77361</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.789312</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.804832</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.853526</v>
       </c>
     </row>
     <row r="93">
@@ -5437,7 +5437,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -6499,7 +6503,11 @@
           <t>Share‐based payments reserve 7</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -7062,7 +7070,11 @@
           <t>Share‐based payment reserves 9</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>2.183365</v>
       </c>
@@ -7370,7 +7382,11 @@
           <t>Share-based payment reserves 9</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>2.183365</v>
       </c>

--- a/output/pdf_financials_xlsx/AUEN.xlsx
+++ b/output/pdf_financials_xlsx/AUEN.xlsx
@@ -729,25 +729,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007585</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.012327</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.021664</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.045488</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.022719</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.005447</v>
       </c>
     </row>
     <row r="13">
@@ -1177,25 +1177,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.058662</v>
+        <v>-2.066247</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.543587</v>
+        <v>-0.555914</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.257302</v>
+        <v>-0.257387</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.779361</v>
+        <v>-0.801025</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-11.156864</v>
+        <v>-11.202352</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.581536</v>
+        <v>-2.604255</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.581536</v>
+        <v>-2.586983</v>
       </c>
     </row>
     <row r="28">
@@ -1233,25 +1233,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.058662</v>
+        <v>-2.066247</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.543587</v>
+        <v>-0.555914</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.257302</v>
+        <v>-0.257387</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.779361</v>
+        <v>-0.801025</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-11.156864</v>
+        <v>-11.202352</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.581536</v>
+        <v>-2.604255</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.581536</v>
+        <v>-2.586983</v>
       </c>
     </row>
     <row r="30">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">

--- a/output/pdf_financials_xlsx/AUEN.xlsx
+++ b/output/pdf_financials_xlsx/AUEN.xlsx
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.048924</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.059674</v>
+        <v>0.108598</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.033143</v>
@@ -3230,20 +3230,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>-0.257302</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.779361</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-11.156864</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-2.581536</v>
@@ -3266,20 +3260,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -3302,23 +3290,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>-0.005739</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>-0.009116000000000001</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0.014063</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.001193</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>0</v>
@@ -3338,20 +3320,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
@@ -3374,20 +3350,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>-0.038385</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.009029000000000001</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0.011258</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>-0.005408</v>
@@ -3410,20 +3380,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0.021957</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.021763</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>-0.043829</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>0.005779</v>
@@ -3446,20 +3410,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
@@ -3482,23 +3440,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>-0.022167</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.021676</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-0.018508</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.000371</v>
+        <v>0.001564</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0.038231</v>
@@ -3518,20 +3470,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0.021735</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.302135</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0.015702</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0.01552</v>
@@ -3554,20 +3500,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -3590,20 +3530,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G109" s="3" t="n">
         <v>0</v>
@@ -3626,26 +3560,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.025187</v>
       </c>
     </row>
     <row r="111">
@@ -3662,20 +3590,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>-0.001366</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -3698,20 +3620,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -3734,20 +3650,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
@@ -3770,20 +3680,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -3806,20 +3710,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -3842,20 +3740,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -3878,20 +3770,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>0</v>
@@ -3914,20 +3800,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0.003503</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>10.861646</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>2.186923</v>
@@ -3950,25 +3830,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>-1.864332</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.759491</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>-0.685549</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>-0.210684</v>
       </c>
       <c r="H119" s="3" t="n">
         <v>-0.048972</v>
@@ -3988,20 +3860,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -4024,20 +3890,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -4060,20 +3920,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>0</v>
@@ -4096,20 +3950,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
@@ -4132,20 +3980,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -4168,20 +4010,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -4204,20 +4040,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
@@ -4282,20 +4112,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
@@ -4318,25 +4142,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>3.44325</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H129" s="3" t="n">
         <v>0.45525</v>
@@ -4398,20 +4214,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
@@ -4434,20 +4244,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>1.093903</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-1.316038</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-1.17445</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>-0.587862</v>
@@ -4512,20 +4316,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>-0.001366</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -4548,20 +4346,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-0.485015</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.556547</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>-0.490267</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.377178</v>
@@ -4581,7 +4373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K188"/>
+  <dimension ref="A1:K215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7642,20 +7434,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="5" t="n">
+        <v>-0.257302</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>-0.779361</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>-11.156864</v>
       </c>
       <c r="J62" s="5" t="n">
         <v>-2.581536</v>
@@ -7700,15 +7486,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H63" s="5" t="n">
+        <v>0.000419</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0.00058</v>
       </c>
       <c r="J63" s="5" t="n">
         <v>0.000351</v>
@@ -7733,7 +7515,11 @@
           <t>Convertible debenture accretion expense</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -7802,15 +7588,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H65" s="5" t="n">
+        <v>0.003503</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>10.861646</v>
       </c>
       <c r="J65" s="5" t="n">
         <v>2.186923</v>
@@ -7855,15 +7637,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H66" s="5" t="n">
+        <v>0.302135</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.015702</v>
       </c>
       <c r="J66" s="5" t="n">
         <v>0.01552</v>
@@ -7955,15 +7733,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H68" s="5" t="n">
+        <v>0.009029000000000001</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.011258</v>
       </c>
       <c r="J68" s="5" t="n">
         <v>-0.005408</v>
@@ -8057,15 +7831,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H70" s="5" t="n">
+        <v>0.018564</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>-0.043829</v>
       </c>
       <c r="J70" s="5" t="n">
         <v>0.005779</v>
@@ -8108,15 +7878,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H71" s="5" t="n">
+        <v>-0.556547</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>-0.488901</v>
       </c>
       <c r="J71" s="5" t="n">
         <v>-0.377178</v>
@@ -8686,17 +8452,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Net loss for the year $ (543,587) $</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>-2.058662</v>
+          <t>Deferred tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8708,15 +8480,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H83" s="5" t="n">
+        <v>0.032644</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>-0.191457</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -8737,21 +8505,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Settlement of flow‐through share premium                           (60,156)                               ‐</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Stock‐based compensation 208,915</t>
+          <t>GST receivable</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>0.352781</v>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8763,20 +8533,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>-0.009116000000000001</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0.014063</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0.001193</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -8792,21 +8556,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Settlement of flow‐through share premium                           (60,156)                               ‐</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 3,697</t>
+          <t>Purchase of equipment</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>1.536096</v>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8823,10 +8589,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="5" t="n">
+        <v>-0.001366</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -8847,17 +8611,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Changes in non‐cash working capital</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Accounts Receivable (33,555)</t>
+          <t>Cash asset transferred to Thunderbird Mineral Corp.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>-0.033313</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8874,10 +8640,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I86" s="5" t="n">
+        <v>-0.355</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -8898,21 +8662,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Changes in non‐cash working capital</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits 32,608</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>-0.039241</v>
+          <t>Thunderbird Mineral Corp. exploration assets additions</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8929,10 +8691,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="5" t="n">
+        <v>-0.038891</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -8953,46 +8713,36 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Changes in non‐cash working capital</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Trade payables and accrued liabilities 21,738</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>0.014477</v>
+          <t>Exploration and evaluation asset additions</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G88" s="5" t="n">
+        <v>-1.864332</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>-0.759491</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>-0.290292</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>-0.210684</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -9008,42 +8758,38 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Changes in non‐cash working capital</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities (366,675)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
-        <v>-0.227862</v>
+        <v>-1.668195</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G89" s="5" t="n">
+        <v>-1.864332</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>-0.759491</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>-0.685549</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.210684</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -9059,17 +8805,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Purchase of equipment                                                 (7,848)                               ‐</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets (788,778)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>-1.668195</v>
+          <t>Change in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9081,20 +8833,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H90" s="5" t="n">
+        <v>-1.316038</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>-1.17445</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>-0.587862</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -9110,17 +8856,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Purchase of equipment                                                 (7,848)                               ‐</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities (796,626)</t>
+          <t>Cash and cash equivalents, beginning</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>-1.668195</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9132,20 +8880,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H91" s="5" t="n">
+        <v>3.426767</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>2.110729</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0.936279</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -9161,17 +8903,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Private placement, net issuance cost 2,028,268</t>
+          <t>Cash and cash equivalents, ending $</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="n">
-        <v>3.116225</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9183,20 +8927,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H92" s="5" t="n">
+        <v>2.110729</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0.936279</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>0.348417</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -9212,46 +8950,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Warrant exercised                                                46,882                               ‐</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Net cash flows from financing activities 2,075,150</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Cash $</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" s="5" t="n">
-        <v>3.116225</v>
+        <v>0.000606</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>3.418267</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>2.102229</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0.927779</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0.339917</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -9267,21 +8993,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Warrant exercised                                                46,882                               ‐</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Increase in cash and cash equivalents 911,849</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>1.220168</v>
+          <t>Guaranteed investment certificate</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9293,20 +9017,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H94" s="5" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -9322,12 +9040,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning                                1,220,168                               ‐</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, ending $ 2,132,017 $</t>
+          <t>Cash and cash equivalents consist of total</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -9339,25 +9057,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G95" s="5" t="n">
+        <v>3.426767</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>2.110729</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0.936279</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0.348417</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -9373,17 +9083,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents consist of</t>
+          <t>Exploration and evaluation assets distributed to the Company’s</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cash $ 1,535,348 $</t>
+          <t>Exploration and evaluation assets distributed to the Company’s shareholders (Note 4) $</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" s="5" t="n">
-        <v>0.000606</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9400,10 +9112,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="5" t="n">
+        <v>0.740218</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -9424,17 +9134,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents consist of</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GIC 596,669</t>
+          <t>Settlement of flow-through share premium</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>1.219562</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9446,10 +9158,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H97" s="5" t="n">
+        <v>-0.134364</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -9475,17 +9185,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents consist of</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents consist of total</t>
+          <t>Fair value of common shares issued for acquisition cost of an exploration and evaluation asset $</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" s="5" t="n">
-        <v>1.220168</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9497,10 +9209,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H98" s="5" t="n">
+        <v>0.07464999999999999</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -9526,12 +9236,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures included in trade</t>
+          <t>Exploration and evaluation expenditures included in accounts</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures included in trade payables $ ‐ $</t>
+          <t>Exploration and evaluation expenditures included in accounts payable $</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -9539,8 +9249,10 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n">
-        <v>0.045197</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9552,10 +9264,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H99" s="5" t="n">
+        <v>0.003199</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -9581,32 +9291,34 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures included in due to</t>
+          <t>Adjustments for non‐cash items</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures included in due to related parties $ ‐ $</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
-        <v>0.06698900000000001</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="5" t="n">
+        <v>0.000905</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>0.000419</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -9632,32 +9344,30 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures included in due to</t>
+          <t>Impairment of exploration and evaluation asset                              3,503                               ‐</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Settlement of flow‐through share premium</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" s="5" t="n">
-        <v>6e-06</v>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="5" t="n">
+        <v>-0.386999</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>-0.134364</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -9683,36 +9393,34 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Impairment of exploration and evaluation asset                              3,503                               ‐</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
+          <t>Deferred tax expense</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>-2.058662</v>
+          <t>DeferredTax</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="5" t="n">
+        <v>0.158813</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>0.032644</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -9738,12 +9446,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Impairment of exploration and evaluation asset                              3,503                               ‐</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Share‐based payments</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9751,23 +9459,21 @@
           <t>StockBasedCompensation</t>
         </is>
       </c>
-      <c r="E103" s="5" t="n">
-        <v>0.352781</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" s="5" t="n">
+        <v>0.021735</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.302135</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -9793,12 +9499,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Changes in non‐cash working capital</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>GST receivable</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9806,23 +9512,21 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E104" s="5" t="n">
-        <v>-0.033313</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G104" s="5" t="n">
+        <v>-0.005739</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>-0.009166000000000001</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -9848,32 +9552,34 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non‐cash working capital</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures, net of recoveries</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" s="5" t="n">
-        <v>-1.668195</v>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="5" t="n">
+        <v>-0.038385</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>-0.009029000000000001</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -9899,36 +9605,34 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non‐cash working capital</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
+          <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="n">
-        <v>-1.668195</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="5" t="n">
+        <v>0.021957</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>0.018564</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -9954,32 +9658,34 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non‐cash working capital</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Private placement, net of issuance costs</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" s="5" t="n">
-        <v>3.116225</v>
+          <t>Net cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="5" t="n">
+        <v>-0.485015</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>-0.556547</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -10005,36 +9711,34 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Net cash flows from financing activities                                                              ‐              3,443,250</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Net cash flows from financing activities</t>
+          <t>Change in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="n">
-        <v>3.116225</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G108" s="5" t="n">
+        <v>1.093903</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>-1.316038</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -10060,36 +9764,30 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Net cash flows from financing activities                                                              ‐              3,443,250</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Increase in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>1.220168</v>
+          <t>Cash and cash equivalents, beginning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="5" t="n">
+        <v>2.332864</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>3.426767</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -10115,32 +9813,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents consist of</t>
+          <t>Net cash flows from financing activities                                                              ‐              3,443,250</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cash $</t>
+          <t>Cash and cash equivalents, ending $</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" s="5" t="n">
-        <v>0.000606</v>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="5" t="n">
+        <v>3.426767</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>2.110729</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -10183,15 +9879,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G111" s="5" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -10217,36 +9909,30 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non-cash investing activities</t>
+          <t>Non‐cash investing and financing activities</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures included in trade payables $</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>0.045197</v>
+          <t>Fair value of common shares issued for acquisition cost of a exploration and evaluation asset $</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0.07464999999999999</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10272,32 +9958,30 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Non-cash investing activities</t>
+          <t>Exploration and evaluation expenditures included in accounts</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures included in due to related parties $</t>
+          <t>Exploration and evaluation expenditures included in accounts payables $</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>0.06698900000000001</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G113" s="5" t="n">
+        <v>0.008935999999999999</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>0.003199</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10323,17 +10007,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Non-cash investing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>Net loss for the year $ (543,587) $</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" s="5" t="n">
-        <v>7e-06</v>
+        <v>-2.058662</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10369,20 +10053,26 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Settlement of flow‐through share premium                           (60,156)                               ‐</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Note December 31, 2025 December</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock‐based compensation 208,915</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0.352781</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10404,38 +10094,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J115" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="K115" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Settlement of flow‐through share premium                           (60,156)                               ‐</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Impairment of exploration and evaluation assets 3,697</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>1.536096</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10457,316 +10149,350 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J116" s="5" t="n">
-        <v>0.000351</v>
-      </c>
-      <c r="K116" s="5" t="n">
-        <v>0.000436</v>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non‐cash working capital</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts Receivable (33,555)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>-0.033313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G117" s="5" t="n">
-        <v>0.024012</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I117" s="5" t="n">
-        <v>0.0675</v>
-      </c>
-      <c r="J117" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K117" s="5" t="n">
-        <v>0.0645</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non‐cash working capital</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Prepaid expenses and deposits 32,608</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0.001175</v>
+        <v>-0.039241</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="5" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>0.03662</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>0.006565</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K118" s="5" t="n">
-        <v>0.006223</v>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non‐cash working capital</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
+          <t>Trade payables and accrued liabilities 21,738</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.014477</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G119" s="5" t="n">
-        <v>0.053466</v>
-      </c>
-      <c r="H119" s="5" t="n">
-        <v>0.043157</v>
-      </c>
-      <c r="I119" s="5" t="n">
-        <v>0.052922</v>
-      </c>
-      <c r="J119" s="5" t="n">
-        <v>0.019106</v>
-      </c>
-      <c r="K119" s="5" t="n">
-        <v>0.024216</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Changes in non‐cash working capital</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Management fees 8</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash flows used in operating activities (366,675)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" s="5" t="n">
+        <v>-0.227862</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G120" s="5" t="n">
-        <v>0.218339</v>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>0.24508</v>
-      </c>
-      <c r="I120" s="5" t="n">
-        <v>0.20532</v>
-      </c>
-      <c r="J120" s="5" t="n">
-        <v>0.19632</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>0.24732</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Purchase of equipment                                                 (7,848)                               ‐</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 8</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation assets (788,778)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" s="5" t="n">
+        <v>-1.668195</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G121" s="5" t="n">
-        <v>0.07423</v>
-      </c>
-      <c r="H121" s="5" t="n">
-        <v>0.0946</v>
-      </c>
-      <c r="I121" s="5" t="n">
-        <v>0.074184</v>
-      </c>
-      <c r="J121" s="5" t="n">
-        <v>0.093989</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>0.081606</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Purchase of equipment                                                 (7,848)                               ‐</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash flows used in investing activities (796,626)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" s="5" t="n">
+        <v>-1.668195</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="5" t="n">
-        <v>0.070988</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>0.167231</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>0.10939</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>0.032046</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>0.05281</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Share-based payments 7,8</t>
+          <t>Private placement, net issuance cost 2,028,268</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E123" s="5" t="n">
+        <v>3.116225</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10778,42 +10504,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H123" s="5" t="n">
-        <v>0.302135</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>0.015702</v>
-      </c>
-      <c r="J123" s="5" t="n">
-        <v>0.01552</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>0.062754</v>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Warrant exercised                                                46,882                               ‐</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Net cash flows from financing activities 2,075,150</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.530151</v>
+        <v>3.116225</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10825,40 +10559,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H124" s="5" t="n">
-        <v>0.899242</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>0.5321630000000001</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>0.417332</v>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>0.539865</v>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Warrant exercised                                                46,882                               ‐</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Convertible debenture interest and accretion expense 6</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash and cash equivalents 911,849</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>1.220168</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10885,74 +10629,82 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K125" s="5" t="n">
-        <v>-0.025187</v>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Cash and cash equivalents, beginning                                1,220,168                               ‐</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Cash and cash equivalents, ending $ 2,132,017 $</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" s="5" t="n">
-        <v>0.007585</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>0.012327</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>8.500000000000001e-05</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>0.021664</v>
-      </c>
-      <c r="I126" s="5" t="n">
-        <v>0.045488</v>
-      </c>
-      <c r="J126" s="5" t="n">
-        <v>0.022719</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>0.005447</v>
+        <v>1.220168</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 5</t>
+          <t>Cash $ 1,535,348 $</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E127" s="5" t="n">
+        <v>0.000606</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10964,40 +10716,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H127" s="5" t="n">
-        <v>-0.003503</v>
-      </c>
-      <c r="I127" s="5" t="n">
-        <v>-10.861646</v>
-      </c>
-      <c r="J127" s="5" t="n">
-        <v>-2.186923</v>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>-0.008861000000000001</v>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Cash and cash equivalents consist of</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Service income 4</t>
+          <t>GIC 596,669</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="5" t="n">
+        <v>1.219562</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11024,35 +10782,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K128" s="5" t="n">
-        <v>0.02858</v>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Exploration and evaluation expenditures included in trade</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year</t>
+          <t>Exploration and evaluation expenditures included in trade payables $ ‐ $</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0.045197</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11074,38 +10832,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J129" s="5" t="n">
-        <v>-2.581536</v>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>-0.539886</v>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Exploration and evaluation expenditures included in due to</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation expenditures included in due to related parties $ ‐ $</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" s="5" t="n">
+        <v>0.06698900000000001</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11127,77 +10883,91 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J130" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding,</t>
+          <t>Exploration and evaluation expenditures included in due to</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="5" t="n">
+        <v>6e-06</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G131" s="5" t="n">
-        <v>15.239058</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>19.450877</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>19.674613</v>
-      </c>
-      <c r="J131" s="5" t="n">
-        <v>19.692969</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>20.460655</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 19,674,613 $ 16,131,464 $ 2,789,312 $</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>-2.058662</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11219,34 +10989,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J132" s="5" t="n">
-        <v>3.704497</v>
-      </c>
-      <c r="K132" s="5" t="n">
-        <v>-15.216279</v>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition cost – Rayfield Property 50,000 6,500 -</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>0.352781</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11268,8 +11044,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n">
-        <v>0.0065</v>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -11280,24 +11058,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Share-based payments - - 15,520</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>-0.033313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11319,8 +11099,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J134" s="5" t="n">
-        <v>0.01552</v>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -11331,28 +11113,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation expenditures, net of recoveries</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>-1.668195</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11374,34 +11150,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J135" s="5" t="n">
-        <v>-2.581536</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>-2.581536</v>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2024 19,724,613 16,137,964 2,804,832</t>
+          <t>Private placement, net of issuance costs</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E136" s="5" t="n">
+        <v>3.116225</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11423,34 +11201,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J136" s="5" t="n">
-        <v>1.144981</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>-17.797815</v>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Convertible debenture – issuance - - 7,014</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>3.116225</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11472,8 +11256,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J137" s="5" t="n">
-        <v>0.007014</v>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -11484,24 +11270,26 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Convertible debenture – exercise 4,000,000 447,014</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1.220168</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11523,34 +11311,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J138" s="5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>-0.007014</v>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Non-cash investing activities</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition cost – Rayfield Property 75,000 24,750 -</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation expenditures included in trade payables $</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.045197</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11572,8 +11366,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J139" s="5" t="n">
-        <v>0.02475</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -11584,24 +11380,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Non-cash investing activities</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Shares issued for options exercised 85,000 29,310 (14,060)</t>
+          <t>Exploration and evaluation expenditures included in due to related parties $</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E140" s="5" t="n">
+        <v>0.06698900000000001</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11623,8 +11417,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J140" s="5" t="n">
-        <v>0.01525</v>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -11635,24 +11431,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
+          <t>Non-cash investing activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Share-based payments - - 62,754</t>
+          <t>See accompanying notes to the financial statements</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E141" s="5" t="n">
+        <v>7e-06</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11674,8 +11468,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J141" s="5" t="n">
-        <v>0.062754</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -11689,14 +11485,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2025 23,884,613 $ 16,639,038 $ 2,853,526 $</t>
+          <t>Note December 31, 2025 December</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -11726,10 +11518,10 @@
         </is>
       </c>
       <c r="J142" s="5" t="n">
-        <v>1.154863</v>
+        <v>0.002024</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>-18.337701</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="143">
@@ -11738,13 +11530,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Note December 31, 2024 December</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -11765,16 +11565,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="5" t="n">
-        <v>0.002023</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000351</v>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>0.000436</v>
       </c>
     </row>
     <row r="144">
@@ -11790,12 +11590,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Amortization $</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -11809,21 +11609,19 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.000905</v>
+        <v>0.024012</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>0.000419</v>
+        <v>0.01</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>0.00058</v>
+        <v>0.0675</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>0.000351</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06</v>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>0.0645</v>
       </c>
     </row>
     <row r="145">
@@ -11834,19 +11632,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Loss before tax</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0.001175</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11854,21 +11654,21 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>-0.09848899999999999</v>
+        <v>0.023</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>-0.746717</v>
+        <v>0.03662</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>-11.348321</v>
-      </c>
-      <c r="J145" s="5" t="n">
-        <v>-2.581536</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006565</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>0.006223</v>
       </c>
     </row>
     <row r="146">
@@ -11879,15 +11679,19 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Deferred tax recovery 11</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -11898,28 +11702,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G146" s="5" t="n">
+        <v>0.053466</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>0.043157</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>0.191457</v>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.052922</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>0.019106</v>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>0.024216</v>
       </c>
     </row>
     <row r="147">
@@ -11930,17 +11726,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year $</t>
+          <t>Management fees 8</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -11954,21 +11750,19 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>-0.257302</v>
+        <v>0.218339</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>-0.779361</v>
+        <v>0.24508</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>-11.156864</v>
+        <v>0.20532</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>-2.581536</v>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.19632</v>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>0.24732</v>
       </c>
     </row>
     <row r="148">
@@ -11979,21 +11773,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Office and miscellaneous 8</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="n">
-        <v>-1.4e-07</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12001,21 +11797,19 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.07423</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.0946</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>-5.699999999999999e-07</v>
+        <v>0.074184</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.093989</v>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>0.081606</v>
       </c>
     </row>
     <row r="149">
@@ -12024,13 +11818,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Note December 31, 2023 December</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -12041,26 +11843,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G149" s="5" t="n">
+        <v>0.070988</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>0.002022</v>
+        <v>0.167231</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.10939</v>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>0.032046</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>0.05281</v>
       </c>
     </row>
     <row r="150">
@@ -12071,12 +11867,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Settlement of flow-through share premium 9</t>
+          <t>Share-based payments 7,8</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -12096,22 +11892,16 @@
         </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>0.134364</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.302135</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>0.015702</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>0.062754</v>
       </c>
     </row>
     <row r="151">
@@ -12122,19 +11912,21 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (expense) 11</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>0.530151</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12147,20 +11939,16 @@
         </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>-0.032644</v>
+        <v>0.899242</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>0.191457</v>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5321630000000001</v>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>0.417332</v>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>0.539865</v>
       </c>
     </row>
     <row r="152">
@@ -12169,10 +11957,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Note December 31, 2022 December</t>
+          <t>Convertible debenture interest and accretion expense 6</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -12186,11 +11978,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G152" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="H152" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -12202,10 +11998,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K152" s="5" t="n">
+        <v>-0.025187</v>
       </c>
     </row>
     <row r="153">
@@ -12216,45 +12010,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Rent recovery                                                                                                      ‐                (1,102)</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Share‐based payments 7,8</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>0.007585</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>0.012327</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.021735</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>0.302135</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021664</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>0.045488</v>
+      </c>
+      <c r="J153" s="5" t="n">
+        <v>0.022719</v>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>0.005447</v>
       </c>
     </row>
     <row r="154">
@@ -12265,12 +12053,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Rent recovery                                                                                                      ‐                (1,102)</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Rent recovery                                                                                                      ‐                (1,102) total</t>
+          <t>Impairment of exploration and evaluation assets 5</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -12284,26 +12072,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G154" s="5" t="n">
-        <v>-0.485573</v>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H154" s="5" t="n">
-        <v>-0.899242</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003503</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>-10.861646</v>
+      </c>
+      <c r="J154" s="5" t="n">
+        <v>-2.186923</v>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>-0.008861000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -12319,7 +12103,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Settlement of flow‐through share premium 9</t>
+          <t>Service income 4</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -12333,11 +12117,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G155" s="5" t="n">
-        <v>0.386999</v>
-      </c>
-      <c r="H155" s="5" t="n">
-        <v>0.134364</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -12349,10 +12137,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K155" s="5" t="n">
+        <v>0.02858</v>
       </c>
     </row>
     <row r="156">
@@ -12368,10 +12154,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Deferred tax expense 11</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>Net and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -12382,26 +12172,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G156" s="5" t="n">
-        <v>0.158813</v>
-      </c>
-      <c r="H156" s="5" t="n">
-        <v>0.032644</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J156" s="5" t="n">
+        <v>-2.581536</v>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>-0.539886</v>
       </c>
     </row>
     <row r="157">
@@ -12412,15 +12202,19 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding,</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>‐ ‐ ‐ ‐ ‐ ‐ statements. (21,204) 21,735 302,135 Reserve 2,470,944</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -12431,26 +12225,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G157" s="5" t="n">
-        <v>2.77361</v>
-      </c>
-      <c r="H157" s="5" t="n">
-        <v>2.471475</v>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J157" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="158">
@@ -12461,45 +12255,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Incorporation on</t>
+          <t>Weighted average number of common shares outstanding,</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Note December 31, 2019 December</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>15.239058</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>19.450877</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>19.674613</v>
+      </c>
+      <c r="J158" s="5" t="n">
+        <v>19.692969</v>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>20.460655</v>
       </c>
     </row>
     <row r="159">
@@ -12510,24 +12298,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Amortization                                      $            3,665     $                       ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="n">
-        <v>0.044221</v>
-      </c>
-      <c r="F159" s="5" t="n">
-        <v>0.049938</v>
+          <t>Balance at December 31, 2023 19,674,613 $ 16,131,464 $ 2,789,312 $</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -12544,15 +12332,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J159" s="5" t="n">
+        <v>3.704497</v>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>-15.216279</v>
       </c>
     </row>
     <row r="160">
@@ -12563,20 +12347,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Amortization                                      $            3,665     $                       ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Management consulting 10</t>
+          <t>Shares issued for acquisition cost – Rayfield Property 50,000 6,500 -</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" s="5" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="F160" s="5" t="n">
-        <v>0.045</v>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -12593,10 +12381,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J160" s="5" t="n">
+        <v>0.0065</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12612,20 +12398,24 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Amortization                                      $            3,665     $                       ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Corporate development and communication 10</t>
+          <t>Share-based payments - - 15,520</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" s="5" t="n">
-        <v>0.016432</v>
-      </c>
-      <c r="F161" s="5" t="n">
-        <v>0.063156</v>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -12642,10 +12432,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J161" s="5" t="n">
+        <v>0.01552</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12661,24 +12449,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Consulting fees                                                   33,153                                 ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Net loss and comprehensive loss for the year - - -</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="n">
-        <v>0.001175</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>0.0025</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -12695,15 +12487,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J162" s="5" t="n">
+        <v>-2.581536</v>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>-2.581536</v>
       </c>
     </row>
     <row r="163">
@@ -12714,24 +12502,24 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Consulting fees                                                   33,153                                 ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 10</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="n">
-        <v>0.029373</v>
-      </c>
-      <c r="F163" s="5" t="n">
-        <v>0.052816</v>
+          <t>Balance at December 31, 2024 19,724,613 16,137,964 2,804,832</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -12748,15 +12536,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J163" s="5" t="n">
+        <v>1.144981</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>-17.797815</v>
       </c>
     </row>
     <row r="164">
@@ -12767,24 +12551,24 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Consulting fees                                                   33,153                                 ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Professional fees 10</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E164" s="5" t="n">
-        <v>0.057269</v>
-      </c>
-      <c r="F164" s="5" t="n">
-        <v>0.123739</v>
+          <t>Convertible debenture – issuance - - 7,014</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -12801,10 +12585,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J164" s="5" t="n">
+        <v>0.007014</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12820,24 +12602,24 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Consulting fees                                                   33,153                                 ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="n">
-        <v>0.01015</v>
-      </c>
-      <c r="F165" s="5" t="n">
-        <v>0.029491</v>
+          <t>Convertible debenture – exercise 4,000,000 447,014</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -12854,15 +12636,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J165" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>-0.007014</v>
       </c>
     </row>
     <row r="166">
@@ -12873,20 +12651,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Consulting fees                                                   33,153                                 ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Stock‐based compensation 9, 10</t>
+          <t>Shares issued for acquisition cost – Rayfield Property 75,000 24,750 -</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" s="5" t="n">
-        <v>0.352781</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>0.208915</v>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -12903,10 +12685,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J166" s="5" t="n">
+        <v>0.02475</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12922,20 +12702,24 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Consulting fees                                                   33,153                                 ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Consulting fees                                                   33,153                                 ‐ total</t>
+          <t>Shares issued for options exercised 85,000 29,310 (14,060)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" s="5" t="n">
-        <v>-0.530151</v>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>-0.6123729999999999</v>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -12952,10 +12736,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J167" s="5" t="n">
+        <v>0.01525</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12971,20 +12753,24 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Settlement of flow‐through share premium        12                60,156                                 ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 7</t>
+          <t>Share-based payments - - 62,754</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" s="5" t="n">
-        <v>-1.536096</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>-0.003697</v>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -13001,10 +12787,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J168" s="5" t="n">
+        <v>0.062754</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -13020,24 +12804,24 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Settlement of flow‐through share premium        12                60,156                                 ‐</t>
+          <t>Shares         Amount       Payments Reserve            Deficit                  Total</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="n">
-        <v>-2.058662</v>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>-0.543587</v>
+          <t>Balance at December 31, 2025 23,884,613 $ 16,639,038 $ 2,853,526 $</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -13054,15 +12838,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J169" s="5" t="n">
+        <v>1.154863</v>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>-18.337701</v>
       </c>
     </row>
     <row r="170">
@@ -13071,26 +12851,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Settlement of flow‐through share premium        12                60,156                                 ‐</t>
-        </is>
-      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E170" s="5" t="n">
-        <v>-5.5e-07</v>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>-1.3e-07</v>
+          <t>Note December 31, 2024 December</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -13102,15 +12878,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I170" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="J170" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -13126,40 +12898,40 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted 9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" s="5" t="n">
-        <v>3.757925</v>
-      </c>
-      <c r="F171" s="5" t="n">
-        <v>4.104513</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization $</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.000905</v>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>0.000419</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="J171" s="5" t="n">
+        <v>0.000351</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -13175,40 +12947,36 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements                               4</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>5                                                                                                           11,398,503             2,039,169 ‐   46,882    (108,031)   208,915 ‐    (543,587)     13,041,851         ‐ ‐    9,988,159             3,116,225   352,781     (2,058,662)     11,398,503                                              Total                                                                                                                Total</t>
+          <t>Loss before tax</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" s="5" t="n">
-        <v>-2.058662</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>-2.058662</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>-0.09848899999999999</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>-0.746717</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>-11.348321</v>
+      </c>
+      <c r="J172" s="5" t="n">
+        <v>-2.581536</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -13224,20 +12992,24 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Deficit                                                                                                                                                             Deficit</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>468 ‐ (24,322) ‐ 208,915 (48,875) ‐ ‐ ‐ ‐ 352,781 ‐ Reserve 2,183,365 2,319,551 Reserve</t>
+          <t>Deferred tax recovery 11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" s="5" t="n">
-        <v>2.183365</v>
-      </c>
-      <c r="F173" s="5" t="n">
-        <v>1.830584</v>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -13249,10 +13021,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I173" s="5" t="n">
+        <v>0.191457</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -13273,46 +13043,40 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Listing and filing fees $</t>
+          <t>Net and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="n">
-        <v>0.044221</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G174" s="5" t="n">
+        <v>-0.257302</v>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>-0.779361</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>-11.156864</v>
+      </c>
+      <c r="J174" s="5" t="n">
+        <v>-2.581536</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13328,42 +13092,38 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Management consulting 10</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E175" s="5" t="n">
-        <v>0.01875</v>
+        <v>-1.4e-07</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G175" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>-5.699999999999999e-07</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>-1.3e-07</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13377,19 +13137,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Corporate development and communication 10</t>
+          <t>Note December 31, 2023 December</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" s="5" t="n">
-        <v>0.016432</v>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13401,15 +13159,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H176" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -13430,21 +13184,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="n">
-        <v>0.029373</v>
+          <t>Settlement of flow-through share premium 9</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13456,10 +13208,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H177" s="5" t="n">
+        <v>0.134364</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -13485,21 +13235,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Professional fees 10</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="n">
-        <v>0.057269</v>
+          <t>Deferred tax recovery (expense) 11</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13511,15 +13259,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H178" s="5" t="n">
+        <v>-0.032644</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>0.191457</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -13538,38 +13282,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="n">
-        <v>0.01015</v>
+          <t>Note December 31, 2022 December</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G179" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -13595,32 +13329,30 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Rent recovery                                                                                                      ‐                (1,102)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Stock-based compensation 9</t>
+          <t>Share‐based payments 7,8</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" s="5" t="n">
-        <v>0.352781</v>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G180" s="5" t="n">
+        <v>0.021735</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>0.302135</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -13646,32 +13378,30 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Rent recovery                                                                                                      ‐                (1,102)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 7</t>
+          <t>Rent recovery                                                                                                      ‐                (1,102) total</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" s="5" t="n">
-        <v>-1.536096</v>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G181" s="5" t="n">
+        <v>-0.485573</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>-0.899242</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -13702,31 +13432,25 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E182" s="5" t="n">
-        <v>-2.058662</v>
+          <t>Settlement of flow‐through share premium 9</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G182" s="5" t="n">
+        <v>0.386999</v>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>0.134364</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -13757,27 +13481,25 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+          <t>Deferred tax expense 11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" s="5" t="n">
-        <v>15.243415</v>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G183" s="5" t="n">
+        <v>0.158813</v>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>0.032644</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -13803,32 +13525,30 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Weighted average number of common shares outstanding,</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements</t>
+          <t>‐ ‐ ‐ ‐ ‐ ‐ statements. (21,204) 21,735 302,135 Reserve 2,470,944</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" s="5" t="n">
-        <v>5e-06</v>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G184" s="5" t="n">
+        <v>2.77361</v>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>2.471475</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -13854,22 +13574,20 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Incorporation on</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Total - - 9,988,159 3,116,225 352,781 (2,058,662) 11,398,503</t>
+          <t>Note December 31, 2019 December</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" s="5" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002018</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -13905,24 +13623,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Amortization                                      $            3,665     $                       ‐</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Other items total</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>0.044221</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>0.049938</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -13958,22 +13676,20 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Amortization                                      $            3,665     $                       ‐</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Deficit (2,058,662)</t>
+          <t>Management consulting 10</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" s="5" t="n">
-        <v>-2.058662</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01875</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>0.045</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -14009,44 +13725,1441 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>shares                                   27,191,915     10,387,336                                   37,579,252                                                        Number</t>
+          <t>Amortization                                      $            3,665     $                       ‐</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>shares                                   27,191,915     10,387,336                                   37,579,252                                                        Number total</t>
+          <t>Corporate development and communication 10</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" s="5" t="n">
+        <v>0.016432</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>0.063156</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Consulting fees                                                   33,153                                 ‐</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>0.001175</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Consulting fees                                                   33,153                                 ‐</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous 10</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="n">
+        <v>0.029373</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>0.052816</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Consulting fees                                                   33,153                                 ‐</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Professional fees 10</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n">
+        <v>0.057269</v>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>0.123739</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Consulting fees                                                   33,153                                 ‐</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>0.029491</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Consulting fees                                                   33,153                                 ‐</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Stock‐based compensation 9, 10</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" s="5" t="n">
+        <v>0.352781</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>0.208915</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Consulting fees                                                   33,153                                 ‐</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Consulting fees                                                   33,153                                 ‐ total</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" s="5" t="n">
+        <v>-0.530151</v>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>-0.6123729999999999</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Settlement of flow‐through share premium        12                60,156                                 ‐</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets 7</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" s="5" t="n">
+        <v>-1.536096</v>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>-0.003697</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Settlement of flow‐through share premium        12                60,156                                 ‐</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="n">
+        <v>-2.058662</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>-0.543587</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Settlement of flow‐through share premium        12                60,156                                 ‐</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="n">
+        <v>-5.5e-07</v>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding, basic and diluted 9</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" s="5" t="n">
+        <v>3.757925</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>4.104513</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>See accompanying notes to the financial statements                               4</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>5                                                                                                           11,398,503             2,039,169 ‐   46,882    (108,031)   208,915 ‐    (543,587)     13,041,851         ‐ ‐    9,988,159             3,116,225   352,781     (2,058,662)     11,398,503                                              Total                                                                                                                Total</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" s="5" t="n">
+        <v>-2.058662</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>-2.058662</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Deficit                                                                                                                                                             Deficit</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>468 ‐ (24,322) ‐ 208,915 (48,875) ‐ ‐ ‐ ‐ 352,781 ‐ Reserve 2,183,365 2,319,551 Reserve</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" s="5" t="n">
+        <v>2.183365</v>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>1.830584</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Listing and filing fees $</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="n">
+        <v>0.044221</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Management consulting 10</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" s="5" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Corporate development and communication 10</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" s="5" t="n">
+        <v>0.016432</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="n">
+        <v>0.029373</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Professional fees 10</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="n">
+        <v>0.057269</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 9</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.352781</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets 7</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>-1.536096</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>-2.058662</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="5" t="n">
+        <v>15.243415</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>See accompanying notes to the financial statements</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Total - - 9,988,159 3,116,225 352,781 (2,058,662) 11,398,503</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>6e-06</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Other items total</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Deficit (2,058,662)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" s="5" t="n">
+        <v>-2.058662</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>shares                                   27,191,915     10,387,336                                   37,579,252                                                        Number</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>shares                                   27,191,915     10,387,336                                   37,579,252                                                        Number total</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="5" t="n">
         <v>9e-06</v>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
